--- a/Assets/Samples/IAPDemo/Excels/Networks/HostKeys/NetworkHostKeys.xlsx
+++ b/Assets/Samples/IAPDemo/Excels/Networks/HostKeys/NetworkHostKeys.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SoloGames-X\nova\Assets\Samples\IAPDemo\Excels\Networks\HostKeys\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61166E6D-1C61-4CED-9E71-6A525CFCDF9F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A61A0F43-4843-44D9-9DCC-41DC45F459BE}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="8130" yWindow="3060" windowWidth="24080" windowHeight="13160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="25">
   <si>
     <t>##comment</t>
   </si>
@@ -90,18 +90,6 @@
   </si>
   <si>
     <t>https://t-pay-v3.ahameet.com</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>ThirdOpenServer</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>游戏第三方打开的url域名</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://t-payments.solotopiax.com</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
@@ -630,7 +618,7 @@
         <v>5</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F2" s="5"/>
       <c r="G2" s="5"/>
@@ -699,10 +687,10 @@
         <v>9</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:24" ht="22" customHeight="1" x14ac:dyDescent="0.25">
@@ -762,18 +750,10 @@
       </c>
     </row>
     <row r="9" spans="1:24" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>24</v>
-      </c>
+      <c r="B9" s="8"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
     </row>
     <row r="10" spans="1:24" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="11" spans="1:24" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -820,11 +800,9 @@
     <hyperlink ref="E7" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
     <hyperlink ref="D8" r:id="rId7" xr:uid="{4A9895B5-FA1E-4E9B-8ADC-D73489DFF848}"/>
     <hyperlink ref="E8" r:id="rId8" xr:uid="{4A9895B5-FA1E-4E9B-8ADC-D73489DFF848}"/>
-    <hyperlink ref="D9" r:id="rId9" xr:uid="{06AC7C6F-AF32-4044-A73C-25DBBC2FF81A}"/>
-    <hyperlink ref="E9" r:id="rId10" xr:uid="{06AC7C6F-AF32-4044-A73C-25DBBC2FF81A}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId11"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId9"/>
 </worksheet>
 </file>
 
@@ -883,7 +861,7 @@
         <v>5</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F2" s="5"/>
       <c r="G2" s="5"/>
@@ -952,10 +930,10 @@
         <v>9</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:24" ht="22" customHeight="1" x14ac:dyDescent="0.25">
@@ -1001,18 +979,10 @@
       </c>
     </row>
     <row r="8" spans="1:24" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>24</v>
-      </c>
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
     </row>
     <row r="9" spans="1:24" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="10" spans="1:24" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -1056,9 +1026,7 @@
     <hyperlink ref="D6" r:id="rId3" xr:uid="{00000000-0004-0000-0100-000001000000}"/>
     <hyperlink ref="E6" r:id="rId4" xr:uid="{00000000-0004-0000-0100-000001000000}"/>
     <hyperlink ref="D7" r:id="rId5" xr:uid="{00000000-0004-0000-0100-000002000000}"/>
-    <hyperlink ref="D8" r:id="rId6" xr:uid="{36AA8FA0-9428-43BB-99F6-0B30FB88A3CD}"/>
-    <hyperlink ref="E8" r:id="rId7" xr:uid="{36AA8FA0-9428-43BB-99F6-0B30FB88A3CD}"/>
-    <hyperlink ref="E7" r:id="rId8" xr:uid="{00000000-0004-0000-0100-000002000000}"/>
+    <hyperlink ref="E7" r:id="rId6" xr:uid="{00000000-0004-0000-0100-000002000000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
